--- a/implementation/phase1/monolith/CRM_Datastore_Quickstart_v1.xlsx
+++ b/implementation/phase1/monolith/CRM_Datastore_Quickstart_v1.xlsx
@@ -3240,7 +3240,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3734,9 +3734,132 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>BID-20260331-0001</v>
+      </c>
+      <c r="B13" t="str">
+        <v>BID-20260331-1774937200779</v>
+      </c>
+      <c r="C13" t="str">
+        <v>CUST-0001</v>
+      </c>
+      <c r="D13" t="str">
+        <v>New Bid</v>
+      </c>
+      <c r="E13" t="str">
+        <v>USR-001</v>
+      </c>
+      <c r="F13" t="str">
+        <v>USR-001</v>
+      </c>
+      <c r="G13" t="str">
+        <v>draft</v>
+      </c>
+      <c r="H13" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="I13" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>BID-20260331-0002</v>
+      </c>
+      <c r="B14" t="str">
+        <v>BID-20260331-1774938352379</v>
+      </c>
+      <c r="C14" t="str">
+        <v>CUST-0001</v>
+      </c>
+      <c r="D14" t="str">
+        <v>New Bid</v>
+      </c>
+      <c r="E14" t="str">
+        <v>USR-001</v>
+      </c>
+      <c r="F14" t="str">
+        <v>USR-001</v>
+      </c>
+      <c r="G14" t="str">
+        <v>draft</v>
+      </c>
+      <c r="H14" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="I14" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>BID-20260331-0003</v>
+      </c>
+      <c r="B15" t="str">
+        <v>BID-20260331-1774938622631</v>
+      </c>
+      <c r="C15" t="str">
+        <v>CUST-0001</v>
+      </c>
+      <c r="D15" t="str">
+        <v>New Bid</v>
+      </c>
+      <c r="E15" t="str">
+        <v>USR-001</v>
+      </c>
+      <c r="F15" t="str">
+        <v>USR-001</v>
+      </c>
+      <c r="G15" t="str">
+        <v>draft</v>
+      </c>
+      <c r="H15" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="I15" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M15"/>
   </ignoredErrors>
 </worksheet>
 </file>
